--- a/OmniBlend_Data_Points_Integration_v2.1.xlsx
+++ b/OmniBlend_Data_Points_Integration_v2.1.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="401">
   <si>
     <t>OmniBlend — Data Points &amp; Integration Requirements  |  Aligned with Implementation Lifecycle v1.0  |  Updated March 2026</t>
   </si>
@@ -1257,6 +1257,72 @@
   </si>
   <si>
     <t>Current / Previous State - indicative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  DOCUMENT ASSISTANT (D0–D6 RAG)</t>
+  </si>
+  <si>
+    <t>Document Assistant</t>
+  </si>
+  <si>
+    <t>RAG Document Search (7 Knowledge-Base Docs: D0–D6)</t>
+  </si>
+  <si>
+    <t>Fully built — Ollama LLM + sentence-transformer embeddings; 7 documents chunked and indexed in vector store; real-time RAG pipeline operational</t>
+  </si>
+  <si>
+    <t>Internal document corpus: D0 (RAG Demo Guide, 88 prompts), D1 (Batch Mfg Record), D2 (SCADA Tag Register), D3 (Cybersecurity Risk Assessment), D4 (As-Is/To-Be Process Map), D5 (QC Procedures &amp; Specs), D6 (LIMS Requirements Spec)</t>
+  </si>
+  <si>
+    <t>Vector similarity search: query → embedding → cosine similarity → top-K passage retrieval → Ollama LLM synthesis → structured response with source attribution; POST /api/v1/ai/doc-query</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>BUILT</t>
+  </si>
+  <si>
+    <t>Built (Simulator)</t>
+  </si>
+  <si>
+    <t>§0 — Simulator Shell (Extra Module — not in lifecycle plan)</t>
+  </si>
+  <si>
+    <t>Quick Prompts Library (44 pre-loaded prompts, D0–D6)</t>
+  </si>
+  <si>
+    <t>Fully built — 44 prompts curated across D0–D6; grouped by document in tabbed interface; covers LOBP operations, SCADA, QC, cybersecurity, LIMS, process mapping</t>
+  </si>
+  <si>
+    <t>Internal — curated prompt library per knowledge-base document; no external data source required</t>
+  </si>
+  <si>
+    <t>Pre-configured query buttons trigger document-specific RAG pipeline; tab UI groups prompts by D0–D6 source document; results include passage provenance</t>
+  </si>
+  <si>
+    <t>AI Response with Source Attribution &amp; Typing Effect</t>
+  </si>
+  <si>
+    <t>Fully built — AI responses rendered with real-time typing animation; cited source documents listed per response with document title and section references</t>
+  </si>
+  <si>
+    <t>Internal — Ollama LLM synthesis from retrieved passages; source document metadata (title, section) embedded in each response</t>
+  </si>
+  <si>
+    <t>RAG pipeline output structured with source passage metadata; frontend renders citations as named document cards alongside the streamed response text</t>
+  </si>
+  <si>
+    <t>Knowledge Base Status Tracker (Per-Document Load &amp; Embedding Status)</t>
+  </si>
+  <si>
+    <t>Fully built — real-time status panel shows embedding load status and chunk count per document (D0–D6); visible in Document Assistant UI</t>
+  </si>
+  <si>
+    <t>Internal — document chunking and embedding pipeline; per-document status tracked in backend state; no external integration required</t>
+  </si>
+  <si>
+    <t>GET /api/v1/ai/doc-status returns per-document chunk count and embedding status; frontend renders as a live status dashboard with pass/fail indicators per document</t>
   </si>
 </sst>
 </file>
@@ -3355,7 +3421,7 @@
     </row>
     <row r="49" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>218</v>
+        <v>379</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -3367,124 +3433,124 @@
       <c r="I49" s="4"/>
     </row>
     <row r="50" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>223</v>
+      <c r="A50" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>384</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>15</v>
+        <v>385</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>16</v>
+        <v>386</v>
       </c>
       <c r="H50" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="I50" s="12" t="s">
-        <v>224</v>
+        <v>387</v>
+      </c>
+      <c r="I50" s="17" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>228</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>229</v>
+      <c r="A51" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>392</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>15</v>
+        <v>385</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>16</v>
+        <v>386</v>
       </c>
       <c r="H51" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="I51" s="17" t="s">
-        <v>224</v>
+        <v>387</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>234</v>
+      <c r="A52" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>396</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>15</v>
+        <v>385</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>16</v>
+        <v>386</v>
       </c>
       <c r="H52" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="I52" s="12" t="s">
-        <v>224</v>
+        <v>387</v>
+      </c>
+      <c r="I52" s="17" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>238</v>
-      </c>
-      <c r="E53" s="16" t="s">
-        <v>239</v>
+      <c r="A53" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>400</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>15</v>
+        <v>385</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>16</v>
+        <v>386</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="I53" s="17" t="s">
-        <v>240</v>
+        <v>387</v>
+      </c>
+      <c r="I53" s="12" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -3496,218 +3562,347 @@
       <c r="I54" s="4"/>
     </row>
     <row r="55" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="B55" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="E55" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="G55" s="20" t="s">
-        <v>42</v>
+      <c r="A55" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="H55" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="I55" s="17" t="s">
-        <v>247</v>
+      <c r="I55" s="12" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="F56" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G56" s="18" t="s">
-        <v>30</v>
+      <c r="A56" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="E56" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="H56" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="I56" s="12" t="s">
-        <v>252</v>
+      <c r="I56" s="17" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="E57" s="16" t="s">
-        <v>256</v>
-      </c>
-      <c r="F57" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G57" s="18" t="s">
-        <v>30</v>
+      <c r="A57" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>233</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="H57" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="I57" s="17" t="s">
-        <v>257</v>
+      <c r="I57" s="12" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>260</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="F58" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="G58" s="18" t="s">
-        <v>30</v>
+      <c r="A58" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="E58" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>16</v>
       </c>
       <c r="H58" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="I58" s="12" t="s">
+      <c r="I58" s="17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+    </row>
+    <row r="60" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="C60" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="D60" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="E60" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G60" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="H60" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="I60" s="17" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="F61" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G61" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="H61" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="I61" s="12" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="13" t="s">
+        <v>242</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="C62" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="E62" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="F62" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G62" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="H62" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="I62" s="17" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="F63" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G63" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="H63" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="I63" s="12" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A60" s="86" t="s">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A65" s="86" t="s">
         <v>263</v>
       </c>
-      <c r="B60" s="86"/>
-      <c r="C60" s="86"/>
-      <c r="D60" s="86"/>
-      <c r="E60" s="86"/>
-      <c r="F60" s="86"/>
-      <c r="G60" s="86"/>
-      <c r="H60" s="86"/>
-      <c r="I60" s="86"/>
-    </row>
-    <row r="61" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="11" t="s">
+      <c r="B65" s="86"/>
+      <c r="C65" s="86"/>
+      <c r="D65" s="86"/>
+      <c r="E65" s="86"/>
+      <c r="F65" s="86"/>
+      <c r="G65" s="86"/>
+      <c r="H65" s="86"/>
+      <c r="I65" s="86"/>
+    </row>
+    <row r="66" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B61" s="87" t="s">
+      <c r="B66" s="87" t="s">
         <v>264</v>
       </c>
-      <c r="C61" s="87"/>
-      <c r="D61" s="87"/>
-      <c r="E61" s="87"/>
-      <c r="F61" s="87"/>
-      <c r="G61" s="87"/>
-      <c r="H61" s="87"/>
-      <c r="I61" s="87"/>
-    </row>
-    <row r="62" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="24" t="s">
+      <c r="C66" s="87"/>
+      <c r="D66" s="87"/>
+      <c r="E66" s="87"/>
+      <c r="F66" s="87"/>
+      <c r="G66" s="87"/>
+      <c r="H66" s="87"/>
+      <c r="I66" s="87"/>
+    </row>
+    <row r="67" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="B62" s="88" t="s">
+      <c r="B67" s="88" t="s">
         <v>265</v>
       </c>
-      <c r="C62" s="88"/>
-      <c r="D62" s="88"/>
-      <c r="E62" s="88"/>
-      <c r="F62" s="88"/>
-      <c r="G62" s="88"/>
-      <c r="H62" s="88"/>
-      <c r="I62" s="88"/>
-    </row>
-    <row r="63" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="20" t="s">
+      <c r="C67" s="88"/>
+      <c r="D67" s="88"/>
+      <c r="E67" s="88"/>
+      <c r="F67" s="88"/>
+      <c r="G67" s="88"/>
+      <c r="H67" s="88"/>
+      <c r="I67" s="88"/>
+    </row>
+    <row r="68" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="B63" s="89" t="s">
+      <c r="B68" s="89" t="s">
         <v>266</v>
       </c>
-      <c r="C63" s="89"/>
-      <c r="D63" s="89"/>
-      <c r="E63" s="89"/>
-      <c r="F63" s="89"/>
-      <c r="G63" s="89"/>
-      <c r="H63" s="89"/>
-      <c r="I63" s="89"/>
-    </row>
-    <row r="64" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="25" t="s">
+      <c r="C68" s="89"/>
+      <c r="D68" s="89"/>
+      <c r="E68" s="89"/>
+      <c r="F68" s="89"/>
+      <c r="G68" s="89"/>
+      <c r="H68" s="89"/>
+      <c r="I68" s="89"/>
+    </row>
+    <row r="69" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="B64" s="83" t="s">
+      <c r="B69" s="83" t="s">
         <v>268</v>
       </c>
-      <c r="C64" s="83"/>
-      <c r="D64" s="83"/>
-      <c r="E64" s="83"/>
-      <c r="F64" s="83"/>
-      <c r="G64" s="83"/>
-      <c r="H64" s="83"/>
-      <c r="I64" s="83"/>
-    </row>
-    <row r="65" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="22" t="s">
+      <c r="C69" s="83"/>
+      <c r="D69" s="83"/>
+      <c r="E69" s="83"/>
+      <c r="F69" s="83"/>
+      <c r="G69" s="83"/>
+      <c r="H69" s="83"/>
+      <c r="I69" s="83"/>
+    </row>
+    <row r="70" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="22" t="s">
         <v>269</v>
       </c>
-      <c r="B65" s="84" t="s">
+      <c r="B70" s="84" t="s">
         <v>270</v>
       </c>
-      <c r="C65" s="84"/>
-      <c r="D65" s="84"/>
-      <c r="E65" s="84"/>
-      <c r="F65" s="84"/>
-      <c r="G65" s="84"/>
-      <c r="H65" s="84"/>
-      <c r="I65" s="84"/>
+      <c r="C70" s="84"/>
+      <c r="D70" s="84"/>
+      <c r="E70" s="84"/>
+      <c r="F70" s="84"/>
+      <c r="G70" s="84"/>
+      <c r="H70" s="84"/>
+      <c r="I70" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B64:I64"/>
-    <mergeCell ref="B65:I65"/>
+    <mergeCell ref="B69:I69"/>
+    <mergeCell ref="B70:I70"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A60:I60"/>
-    <mergeCell ref="B61:I61"/>
-    <mergeCell ref="B62:I62"/>
-    <mergeCell ref="B63:I63"/>
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="B66:I66"/>
+    <mergeCell ref="B67:I67"/>
+    <mergeCell ref="B68:I68"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
